--- a/src/results/chile/cross_tab_employment.xlsx
+++ b/src/results/chile/cross_tab_employment.xlsx
@@ -482,16 +482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>367</v>
+        <v>227</v>
       </c>
       <c r="D3" t="n">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="E3" t="n">
-        <v>173</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>628</v>
+        <v>851</v>
       </c>
       <c r="C4" t="n">
-        <v>3218</v>
+        <v>3948</v>
       </c>
       <c r="D4" t="n">
-        <v>3576</v>
+        <v>4425</v>
       </c>
       <c r="E4" t="n">
-        <v>1912</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +520,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="C5" t="n">
-        <v>643</v>
+        <v>469</v>
       </c>
       <c r="D5" t="n">
-        <v>488</v>
+        <v>346</v>
       </c>
       <c r="E5" t="n">
-        <v>318</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>737</v>
+        <v>779</v>
       </c>
       <c r="C6" t="n">
-        <v>2842</v>
+        <v>3168</v>
       </c>
       <c r="D6" t="n">
-        <v>2746</v>
+        <v>2681</v>
       </c>
       <c r="E6" t="n">
-        <v>1679</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>816</v>
+        <v>782</v>
       </c>
       <c r="C7" t="n">
-        <v>2793</v>
+        <v>2644</v>
       </c>
       <c r="D7" t="n">
-        <v>1971</v>
+        <v>1631</v>
       </c>
       <c r="E7" t="n">
-        <v>999</v>
+        <v>897</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>872</v>
+        <v>1034</v>
       </c>
       <c r="C8" t="n">
-        <v>3083</v>
+        <v>3494</v>
       </c>
       <c r="D8" t="n">
-        <v>2031</v>
+        <v>2173</v>
       </c>
       <c r="E8" t="n">
-        <v>995</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +596,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1558</v>
+        <v>1485</v>
       </c>
       <c r="C9" t="n">
-        <v>5056</v>
+        <v>5054</v>
       </c>
       <c r="D9" t="n">
-        <v>3143</v>
+        <v>3210</v>
       </c>
       <c r="E9" t="n">
-        <v>1646</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +615,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2035</v>
+        <v>2201</v>
       </c>
       <c r="C10" t="n">
-        <v>6773</v>
+        <v>8356</v>
       </c>
       <c r="D10" t="n">
-        <v>3880</v>
+        <v>4818</v>
       </c>
       <c r="E10" t="n">
-        <v>1889</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="11">
@@ -634,16 +634,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1560</v>
+        <v>1714</v>
       </c>
       <c r="C11" t="n">
-        <v>6942</v>
+        <v>7574</v>
       </c>
       <c r="D11" t="n">
-        <v>3259</v>
+        <v>4125</v>
       </c>
       <c r="E11" t="n">
-        <v>1363</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="12">
@@ -653,16 +653,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>988</v>
+        <v>913</v>
       </c>
       <c r="C12" t="n">
-        <v>4477</v>
+        <v>5239</v>
       </c>
       <c r="D12" t="n">
-        <v>1612</v>
+        <v>1967</v>
       </c>
       <c r="E12" t="n">
-        <v>871</v>
+        <v>944</v>
       </c>
     </row>
     <row r="14">
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="C16" t="n">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="D16" t="n">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="E16" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -723,16 +723,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>496</v>
+        <v>637</v>
       </c>
       <c r="C17" t="n">
-        <v>2323</v>
+        <v>2675</v>
       </c>
       <c r="D17" t="n">
-        <v>2590</v>
+        <v>3153</v>
       </c>
       <c r="E17" t="n">
-        <v>1221</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="18">
@@ -742,16 +742,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>415</v>
+        <v>283</v>
       </c>
       <c r="D18" t="n">
-        <v>369</v>
+        <v>209</v>
       </c>
       <c r="E18" t="n">
-        <v>208</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19">
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>541</v>
+        <v>609</v>
       </c>
       <c r="C19" t="n">
-        <v>1874</v>
+        <v>2181</v>
       </c>
       <c r="D19" t="n">
-        <v>2143</v>
+        <v>2008</v>
       </c>
       <c r="E19" t="n">
-        <v>1213</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="20">
@@ -780,16 +780,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>747</v>
+        <v>630</v>
       </c>
       <c r="C20" t="n">
-        <v>1926</v>
+        <v>1639</v>
       </c>
       <c r="D20" t="n">
-        <v>1309</v>
+        <v>1150</v>
       </c>
       <c r="E20" t="n">
-        <v>780</v>
+        <v>662</v>
       </c>
     </row>
     <row r="21">
@@ -799,16 +799,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>746</v>
+        <v>966</v>
       </c>
       <c r="C21" t="n">
-        <v>2033</v>
+        <v>2434</v>
       </c>
       <c r="D21" t="n">
-        <v>1521</v>
+        <v>1564</v>
       </c>
       <c r="E21" t="n">
-        <v>856</v>
+        <v>892</v>
       </c>
     </row>
     <row r="22">
@@ -818,16 +818,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1511</v>
+        <v>1425</v>
       </c>
       <c r="C22" t="n">
-        <v>3421</v>
+        <v>3358</v>
       </c>
       <c r="D22" t="n">
-        <v>2409</v>
+        <v>2229</v>
       </c>
       <c r="E22" t="n">
-        <v>1392</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="23">
@@ -837,16 +837,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2216</v>
+        <v>2508</v>
       </c>
       <c r="C23" t="n">
-        <v>4790</v>
+        <v>5983</v>
       </c>
       <c r="D23" t="n">
-        <v>3190</v>
+        <v>4185</v>
       </c>
       <c r="E23" t="n">
-        <v>1891</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="24">
@@ -856,16 +856,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1740</v>
+        <v>1910</v>
       </c>
       <c r="C24" t="n">
-        <v>5189</v>
+        <v>5822</v>
       </c>
       <c r="D24" t="n">
-        <v>2869</v>
+        <v>3674</v>
       </c>
       <c r="E24" t="n">
-        <v>1694</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="25">
@@ -875,16 +875,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1207</v>
+        <v>1156</v>
       </c>
       <c r="C25" t="n">
-        <v>3416</v>
+        <v>3989</v>
       </c>
       <c r="D25" t="n">
-        <v>1568</v>
+        <v>1958</v>
       </c>
       <c r="E25" t="n">
-        <v>1193</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="27">
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="C29" t="n">
-        <v>146</v>
+        <v>80</v>
       </c>
       <c r="D29" t="n">
-        <v>109</v>
+        <v>57</v>
       </c>
       <c r="E29" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -945,16 +945,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>368</v>
+        <v>520</v>
       </c>
       <c r="C30" t="n">
-        <v>1474</v>
+        <v>1954</v>
       </c>
       <c r="D30" t="n">
-        <v>1680</v>
+        <v>2216</v>
       </c>
       <c r="E30" t="n">
-        <v>807</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="31">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>229</v>
+        <v>166</v>
       </c>
       <c r="D31" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="E31" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
@@ -983,16 +983,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>388</v>
+        <v>561</v>
       </c>
       <c r="C32" t="n">
-        <v>1313</v>
+        <v>1645</v>
       </c>
       <c r="D32" t="n">
-        <v>1488</v>
+        <v>1571</v>
       </c>
       <c r="E32" t="n">
-        <v>851</v>
+        <v>875</v>
       </c>
     </row>
     <row r="33">
@@ -1002,16 +1002,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>557</v>
+        <v>523</v>
       </c>
       <c r="C33" t="n">
-        <v>1463</v>
+        <v>1132</v>
       </c>
       <c r="D33" t="n">
-        <v>984</v>
+        <v>748</v>
       </c>
       <c r="E33" t="n">
-        <v>573</v>
+        <v>508</v>
       </c>
     </row>
     <row r="34">
@@ -1021,16 +1021,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>626</v>
+        <v>767</v>
       </c>
       <c r="C34" t="n">
-        <v>1590</v>
+        <v>1882</v>
       </c>
       <c r="D34" t="n">
-        <v>1139</v>
+        <v>1273</v>
       </c>
       <c r="E34" t="n">
-        <v>636</v>
+        <v>683</v>
       </c>
     </row>
     <row r="35">
@@ -1040,16 +1040,16 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1041</v>
+        <v>1060</v>
       </c>
       <c r="C35" t="n">
-        <v>2605</v>
+        <v>2574</v>
       </c>
       <c r="D35" t="n">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="E35" t="n">
-        <v>1007</v>
+        <v>896</v>
       </c>
     </row>
     <row r="36">
@@ -1059,16 +1059,16 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1701</v>
+        <v>2140</v>
       </c>
       <c r="C36" t="n">
-        <v>3603</v>
+        <v>5520</v>
       </c>
       <c r="D36" t="n">
-        <v>2443</v>
+        <v>3415</v>
       </c>
       <c r="E36" t="n">
-        <v>1399</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="37">
@@ -1078,16 +1078,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1853</v>
+        <v>2118</v>
       </c>
       <c r="C37" t="n">
-        <v>5010</v>
+        <v>5899</v>
       </c>
       <c r="D37" t="n">
-        <v>2526</v>
+        <v>3229</v>
       </c>
       <c r="E37" t="n">
-        <v>1473</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="38">
@@ -1097,16 +1097,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1258</v>
+        <v>1417</v>
       </c>
       <c r="C38" t="n">
-        <v>3433</v>
+        <v>4302</v>
       </c>
       <c r="D38" t="n">
-        <v>1345</v>
+        <v>1935</v>
       </c>
       <c r="E38" t="n">
-        <v>1073</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="40">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C42" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="D42" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="E42" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>428</v>
+        <v>580</v>
       </c>
       <c r="C43" t="n">
-        <v>1632</v>
+        <v>1962</v>
       </c>
       <c r="D43" t="n">
-        <v>1971</v>
+        <v>2456</v>
       </c>
       <c r="E43" t="n">
-        <v>940</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="44">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C44" t="n">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D44" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="E44" t="n">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>458</v>
+        <v>563</v>
       </c>
       <c r="C45" t="n">
-        <v>1473</v>
+        <v>1691</v>
       </c>
       <c r="D45" t="n">
-        <v>1746</v>
+        <v>1757</v>
       </c>
       <c r="E45" t="n">
-        <v>968</v>
+        <v>838</v>
       </c>
     </row>
     <row r="46">
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="C46" t="n">
-        <v>1371</v>
+        <v>1090</v>
       </c>
       <c r="D46" t="n">
-        <v>1001</v>
+        <v>832</v>
       </c>
       <c r="E46" t="n">
-        <v>597</v>
+        <v>467</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>723</v>
+        <v>909</v>
       </c>
       <c r="C47" t="n">
-        <v>1765</v>
+        <v>1999</v>
       </c>
       <c r="D47" t="n">
-        <v>1306</v>
+        <v>1338</v>
       </c>
       <c r="E47" t="n">
-        <v>777</v>
+        <v>701</v>
       </c>
     </row>
     <row r="48">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1414</v>
+        <v>1197</v>
       </c>
       <c r="C48" t="n">
-        <v>2959</v>
+        <v>2617</v>
       </c>
       <c r="D48" t="n">
-        <v>2246</v>
+        <v>1872</v>
       </c>
       <c r="E48" t="n">
-        <v>1218</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="49">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2279</v>
+        <v>2545</v>
       </c>
       <c r="C49" t="n">
-        <v>4631</v>
+        <v>5853</v>
       </c>
       <c r="D49" t="n">
-        <v>3220</v>
+        <v>4134</v>
       </c>
       <c r="E49" t="n">
-        <v>1725</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="50">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1801</v>
+        <v>2203</v>
       </c>
       <c r="C50" t="n">
-        <v>4888</v>
+        <v>5676</v>
       </c>
       <c r="D50" t="n">
-        <v>2793</v>
+        <v>3718</v>
       </c>
       <c r="E50" t="n">
-        <v>1493</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="51">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1235</v>
+        <v>1392</v>
       </c>
       <c r="C51" t="n">
-        <v>3358</v>
+        <v>4110</v>
       </c>
       <c r="D51" t="n">
-        <v>1512</v>
+        <v>2043</v>
       </c>
       <c r="E51" t="n">
-        <v>1029</v>
+        <v>1227</v>
       </c>
     </row>
   </sheetData>
@@ -1379,16 +1379,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>279</v>
+        <v>191</v>
       </c>
       <c r="C2" t="n">
-        <v>846</v>
+        <v>523</v>
       </c>
       <c r="D2" t="n">
-        <v>614</v>
+        <v>375</v>
       </c>
       <c r="E2" t="n">
-        <v>357</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1920</v>
+        <v>2588</v>
       </c>
       <c r="C3" t="n">
-        <v>8647</v>
+        <v>10539</v>
       </c>
       <c r="D3" t="n">
-        <v>9817</v>
+        <v>12250</v>
       </c>
       <c r="E3" t="n">
-        <v>4880</v>
+        <v>6470</v>
       </c>
     </row>
     <row r="4">
@@ -1417,16 +1417,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>472</v>
+        <v>322</v>
       </c>
       <c r="C4" t="n">
-        <v>1521</v>
+        <v>1046</v>
       </c>
       <c r="D4" t="n">
-        <v>1205</v>
+        <v>781</v>
       </c>
       <c r="E4" t="n">
-        <v>714</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5">
@@ -1436,16 +1436,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2124</v>
+        <v>2512</v>
       </c>
       <c r="C5" t="n">
-        <v>7502</v>
+        <v>8685</v>
       </c>
       <c r="D5" t="n">
-        <v>8123</v>
+        <v>8017</v>
       </c>
       <c r="E5" t="n">
-        <v>4711</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="6">
@@ -1455,16 +1455,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2681</v>
+        <v>2481</v>
       </c>
       <c r="C6" t="n">
-        <v>7553</v>
+        <v>6505</v>
       </c>
       <c r="D6" t="n">
-        <v>5265</v>
+        <v>4361</v>
       </c>
       <c r="E6" t="n">
-        <v>2949</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="7">
@@ -1474,16 +1474,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2967</v>
+        <v>3676</v>
       </c>
       <c r="C7" t="n">
-        <v>8471</v>
+        <v>9809</v>
       </c>
       <c r="D7" t="n">
-        <v>5997</v>
+        <v>6348</v>
       </c>
       <c r="E7" t="n">
-        <v>3264</v>
+        <v>3293</v>
       </c>
     </row>
     <row r="8">
@@ -1493,16 +1493,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5524</v>
+        <v>5167</v>
       </c>
       <c r="C8" t="n">
-        <v>14041</v>
+        <v>13603</v>
       </c>
       <c r="D8" t="n">
-        <v>9493</v>
+        <v>9009</v>
       </c>
       <c r="E8" t="n">
-        <v>5263</v>
+        <v>4790</v>
       </c>
     </row>
     <row r="9">
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8231</v>
+        <v>9394</v>
       </c>
       <c r="C9" t="n">
-        <v>19797</v>
+        <v>25712</v>
       </c>
       <c r="D9" t="n">
-        <v>12733</v>
+        <v>16552</v>
       </c>
       <c r="E9" t="n">
-        <v>6904</v>
+        <v>8348</v>
       </c>
     </row>
     <row r="10">
@@ -1531,16 +1531,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6954</v>
+        <v>7945</v>
       </c>
       <c r="C10" t="n">
-        <v>22029</v>
+        <v>24971</v>
       </c>
       <c r="D10" t="n">
-        <v>11447</v>
+        <v>14746</v>
       </c>
       <c r="E10" t="n">
-        <v>6023</v>
+        <v>7799</v>
       </c>
     </row>
     <row r="11">
@@ -1550,16 +1550,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4688</v>
+        <v>4878</v>
       </c>
       <c r="C11" t="n">
-        <v>14684</v>
+        <v>17640</v>
       </c>
       <c r="D11" t="n">
-        <v>6037</v>
+        <v>7903</v>
       </c>
       <c r="E11" t="n">
-        <v>4166</v>
+        <v>4812</v>
       </c>
     </row>
   </sheetData>
